--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.40573634522459</v>
+        <v>5.753432156098996</v>
       </c>
       <c r="D2" t="n">
-        <v>35.96653639663739</v>
+        <v>5.844562164453577</v>
       </c>
       <c r="E2" t="n">
-        <v>8.214603529769091</v>
+        <v>1.334873073587477</v>
       </c>
       <c r="F2" t="n">
-        <v>8.243774038447709</v>
+        <v>1.339613281247753</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.39023688904759</v>
+        <v>2.825913494470234</v>
       </c>
       <c r="D3" t="n">
-        <v>17.51963371982067</v>
+        <v>2.846940479470859</v>
       </c>
       <c r="E3" t="n">
-        <v>8.214603529769091</v>
+        <v>1.334873073587477</v>
       </c>
       <c r="F3" t="n">
-        <v>8.243774038447709</v>
+        <v>1.339613281247753</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.51351490498763</v>
+        <v>3.495946172060491</v>
       </c>
       <c r="D4" t="n">
-        <v>21.81553433623687</v>
+        <v>3.545024329638491</v>
       </c>
       <c r="E4" t="n">
-        <v>8.214603529769091</v>
+        <v>1.334873073587477</v>
       </c>
       <c r="F4" t="n">
-        <v>8.243774038447709</v>
+        <v>1.339613281247753</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.46580880355206</v>
+        <v>6.08819393057721</v>
       </c>
       <c r="D5" t="n">
-        <v>37.73634851434993</v>
+        <v>6.132156633581864</v>
       </c>
       <c r="E5" t="n">
-        <v>8.214603529769091</v>
+        <v>1.334873073587477</v>
       </c>
       <c r="F5" t="n">
-        <v>8.243774038447709</v>
+        <v>1.339613281247753</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.86509122084767</v>
+        <v>5.665577323387746</v>
       </c>
       <c r="D6" t="n">
-        <v>34.751870576611</v>
+        <v>5.647178968699288</v>
       </c>
       <c r="E6" t="n">
-        <v>8.214603529769091</v>
+        <v>1.334873073587477</v>
       </c>
       <c r="F6" t="n">
-        <v>8.243774038447709</v>
+        <v>1.339613281247753</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
